--- a/output/pdf_financials_xlsx/DAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/DAQ.P.xlsx
@@ -479,15 +479,11 @@
           <t>Revenue</t>
         </is>
       </c>
-      <c r="B4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C4" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D4" s="1" t="inlineStr">
         <is>
@@ -506,15 +502,11 @@
           <t xml:space="preserve">  Cost of Goods Sold</t>
         </is>
       </c>
-      <c r="B5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D5" s="1" t="inlineStr">
         <is>
@@ -533,15 +525,11 @@
           <t>Gross Profit</t>
         </is>
       </c>
-      <c r="B6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C6" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D6" s="1" t="inlineStr">
         <is>
@@ -560,15 +548,11 @@
           <t xml:space="preserve">  Selling, General, &amp; Admin. Expense</t>
         </is>
       </c>
-      <c r="B7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B7" s="3" t="n">
+        <v>0.032287</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>0.012313</v>
       </c>
       <c r="D7" s="1" t="inlineStr">
         <is>
@@ -587,15 +571,11 @@
           <t xml:space="preserve">  Research &amp; Development</t>
         </is>
       </c>
-      <c r="B8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C8" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D8" s="1" t="inlineStr">
         <is>
@@ -614,15 +594,11 @@
           <t xml:space="preserve">  Other Operating Expense</t>
         </is>
       </c>
-      <c r="B9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D9" s="1" t="inlineStr">
         <is>
@@ -641,15 +617,11 @@
           <t xml:space="preserve">  Total Operating Expense</t>
         </is>
       </c>
-      <c r="B10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B10" s="3" t="n">
+        <v>0.192184</v>
+      </c>
+      <c r="C10" s="3" t="n">
+        <v>0.064777</v>
       </c>
       <c r="D10" s="1" t="inlineStr">
         <is>
@@ -668,15 +640,11 @@
           <t>Operating Income</t>
         </is>
       </c>
-      <c r="B11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B11" s="3" t="n">
+        <v>-0.192184</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>-0.064777</v>
       </c>
       <c r="D11" s="1" t="inlineStr">
         <is>
@@ -695,15 +663,11 @@
           <t xml:space="preserve">    Interest Income</t>
         </is>
       </c>
-      <c r="B12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D12" s="1" t="inlineStr">
         <is>
@@ -722,15 +686,11 @@
           <t xml:space="preserve">    Interest Expense</t>
         </is>
       </c>
-      <c r="B13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B13" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D13" s="1" t="inlineStr">
         <is>
@@ -749,15 +709,11 @@
           <t xml:space="preserve">  Net Interest Income</t>
         </is>
       </c>
-      <c r="B14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C14" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D14" s="1" t="inlineStr">
         <is>
@@ -776,15 +732,11 @@
           <t xml:space="preserve">  Other Income (Expense)</t>
         </is>
       </c>
-      <c r="B15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B15" s="3" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="C15" s="3" t="n">
+        <v>-1e-06</v>
       </c>
       <c r="D15" s="1" t="inlineStr">
         <is>
@@ -803,15 +755,11 @@
           <t>Pretax Income</t>
         </is>
       </c>
-      <c r="B16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B16" s="3" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="C16" s="3" t="n">
+        <v>-0.192185</v>
       </c>
       <c r="D16" s="1" t="inlineStr">
         <is>
@@ -830,15 +778,11 @@
           <t xml:space="preserve">  Tax Provision</t>
         </is>
       </c>
-      <c r="B17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B17" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C17" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D17" s="1" t="inlineStr">
         <is>
@@ -911,15 +855,11 @@
           <t xml:space="preserve">    Net Income (Continuing Operations)</t>
         </is>
       </c>
-      <c r="B20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B20" s="3" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="C20" s="3" t="n">
+        <v>-0.192185</v>
       </c>
       <c r="D20" s="1" t="inlineStr">
         <is>
@@ -938,15 +878,11 @@
           <t xml:space="preserve">    Net Income (Discontinued Operations)</t>
         </is>
       </c>
-      <c r="B21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C21" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D21" s="1" t="inlineStr">
         <is>
@@ -965,15 +901,11 @@
           <t xml:space="preserve">  Other Income (Minority Interest)</t>
         </is>
       </c>
-      <c r="B22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D22" s="1" t="inlineStr">
         <is>
@@ -1038,15 +970,11 @@
           <t>EPS (Diluted)</t>
         </is>
       </c>
-      <c r="B25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B25" s="3" t="n">
+        <v>-0.03</v>
+      </c>
+      <c r="C25" s="3" t="n">
+        <v>-0.01</v>
       </c>
       <c r="D25" s="1" t="inlineStr">
         <is>
@@ -1065,10 +993,8 @@
           <t>Shares Outstanding (Diluted Average)</t>
         </is>
       </c>
-      <c r="B26" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B26" s="3" t="n">
+        <v>6.406167</v>
       </c>
       <c r="C26" s="1" t="inlineStr">
         <is>
@@ -1092,15 +1018,11 @@
           <t>EBIT</t>
         </is>
       </c>
-      <c r="B27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B27" s="3" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="C27" s="3" t="n">
+        <v>-0.192185</v>
       </c>
       <c r="D27" s="1" t="inlineStr">
         <is>
@@ -1119,15 +1041,11 @@
           <t xml:space="preserve">  Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C28" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D28" s="1" t="inlineStr">
         <is>
@@ -1146,15 +1064,11 @@
           <t>EBITDA</t>
         </is>
       </c>
-      <c r="B29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B29" s="3" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="C29" s="3" t="n">
+        <v>-0.192185</v>
       </c>
       <c r="D29" s="1" t="inlineStr">
         <is>
@@ -1200,15 +1114,11 @@
           <t>Tax Rate %</t>
         </is>
       </c>
-      <c r="B31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="C31" s="3" t="n">
+        <v>-0</v>
       </c>
       <c r="D31" s="1" t="inlineStr">
         <is>
@@ -1261,25 +1171,17 @@
           <t xml:space="preserve">    Cash and Cash Equivalents</t>
         </is>
       </c>
-      <c r="B34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E34" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E34" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="35">
@@ -1288,25 +1190,17 @@
           <t xml:space="preserve">    Marketable Securities</t>
         </is>
       </c>
-      <c r="B35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E35" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D35" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="36">
@@ -1315,25 +1209,17 @@
           <t xml:space="preserve">  Cash, Cash Equivalents, Marketable Securities</t>
         </is>
       </c>
-      <c r="B36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E36" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D36" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="37">
@@ -1342,25 +1228,17 @@
           <t xml:space="preserve">    Accounts Receivable</t>
         </is>
       </c>
-      <c r="B37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E37" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="38">
@@ -1369,25 +1247,17 @@
           <t xml:space="preserve">    Notes Receivable</t>
         </is>
       </c>
-      <c r="B38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E38" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E38" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="39">
@@ -1396,25 +1266,17 @@
           <t xml:space="preserve">    Loans Receivable</t>
         </is>
       </c>
-      <c r="B39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E39" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D39" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="40">
@@ -1423,25 +1285,17 @@
           <t xml:space="preserve">    Other Current Receivables</t>
         </is>
       </c>
-      <c r="B40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E40" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B40" s="3" t="n">
+        <v>0.005463</v>
+      </c>
+      <c r="C40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D40" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E40" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="41">
@@ -1450,25 +1304,17 @@
           <t xml:space="preserve">  Total Receivables</t>
         </is>
       </c>
-      <c r="B41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E41" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B41" s="3" t="n">
+        <v>0.005463</v>
+      </c>
+      <c r="C41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="42">
@@ -1477,25 +1323,17 @@
           <t xml:space="preserve">    Inventories, Raw Materials &amp; Components</t>
         </is>
       </c>
-      <c r="B42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E42" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="43">
@@ -1504,25 +1342,17 @@
           <t xml:space="preserve">    Inventories, Work In Process</t>
         </is>
       </c>
-      <c r="B43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E43" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="44">
@@ -1531,25 +1361,17 @@
           <t xml:space="preserve">    Inventories, Inventories Adjustments</t>
         </is>
       </c>
-      <c r="B44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E44" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="45">
@@ -1558,25 +1380,17 @@
           <t xml:space="preserve">    Inventories, Finished Goods</t>
         </is>
       </c>
-      <c r="B45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E45" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="46">
@@ -1585,25 +1399,17 @@
           <t xml:space="preserve">    Inventories, Other</t>
         </is>
       </c>
-      <c r="B46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E46" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E46" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="47">
@@ -1612,25 +1418,17 @@
           <t xml:space="preserve">  Total Inventories</t>
         </is>
       </c>
-      <c r="B47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E47" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E47" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="48">
@@ -1639,25 +1437,17 @@
           <t xml:space="preserve">  Other Current Assets</t>
         </is>
       </c>
-      <c r="B48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E48" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="49">
@@ -1693,25 +1483,17 @@
           <t xml:space="preserve">  Investments And Advances</t>
         </is>
       </c>
-      <c r="B50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E50" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="51">
@@ -1720,25 +1502,17 @@
           <t xml:space="preserve">      Land And Improvements</t>
         </is>
       </c>
-      <c r="B51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E51" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="52">
@@ -1747,25 +1521,17 @@
           <t xml:space="preserve">      Buildings And Improvements</t>
         </is>
       </c>
-      <c r="B52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E52" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E52" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="53">
@@ -1774,25 +1540,17 @@
           <t xml:space="preserve">      Machinery, Furniture, Equipment</t>
         </is>
       </c>
-      <c r="B53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E53" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="54">
@@ -1801,25 +1559,17 @@
           <t xml:space="preserve">      Construction In Progress</t>
         </is>
       </c>
-      <c r="B54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E54" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -1855,25 +1605,17 @@
           <t xml:space="preserve">    Gross Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E56" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="57">
@@ -1882,25 +1624,17 @@
           <t xml:space="preserve">    Accumulated Depreciation</t>
         </is>
       </c>
-      <c r="B57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E57" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -1909,25 +1643,17 @@
           <t xml:space="preserve">  Property, Plant and Equipment</t>
         </is>
       </c>
-      <c r="B58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E58" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="59">
@@ -1936,25 +1662,17 @@
           <t xml:space="preserve">  Intangible Assets</t>
         </is>
       </c>
-      <c r="B59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E59" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="60">
@@ -1963,25 +1681,17 @@
           <t xml:space="preserve">    Goodwill</t>
         </is>
       </c>
-      <c r="B60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E60" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D60" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="61">
@@ -1990,25 +1700,17 @@
           <t xml:space="preserve">  Other Long Term Assets</t>
         </is>
       </c>
-      <c r="B61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E61" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -2063,25 +1765,17 @@
           <t xml:space="preserve">    Accounts Payable</t>
         </is>
       </c>
-      <c r="B64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E64" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E64" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="65">
@@ -2090,25 +1784,17 @@
           <t xml:space="preserve">    Total Tax Payable</t>
         </is>
       </c>
-      <c r="B65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E65" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D65" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="66">
@@ -2117,25 +1803,17 @@
           <t xml:space="preserve">    Other Current Payables</t>
         </is>
       </c>
-      <c r="B66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E66" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="67">
@@ -2144,25 +1822,17 @@
           <t xml:space="preserve">    Current Accrued Expense</t>
         </is>
       </c>
-      <c r="B67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E67" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B67" s="3" t="n">
+        <v>0.021836</v>
+      </c>
+      <c r="C67" s="3" t="n">
+        <v>0.026394</v>
+      </c>
+      <c r="D67" s="3" t="n">
+        <v>0.035445</v>
+      </c>
+      <c r="E67" s="3" t="n">
+        <v>0.039283</v>
       </c>
     </row>
     <row r="68">
@@ -2171,25 +1841,17 @@
           <t xml:space="preserve">  Accounts Payable &amp; Accrued Expense</t>
         </is>
       </c>
-      <c r="B68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E68" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B68" s="3" t="n">
+        <v>0.021836</v>
+      </c>
+      <c r="C68" s="3" t="n">
+        <v>0.026394</v>
+      </c>
+      <c r="D68" s="3" t="n">
+        <v>0.035445</v>
+      </c>
+      <c r="E68" s="3" t="n">
+        <v>0.039283</v>
       </c>
     </row>
     <row r="69">
@@ -2198,25 +1860,17 @@
           <t xml:space="preserve">    Short-Term Debt</t>
         </is>
       </c>
-      <c r="B69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E69" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E69" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="70">
@@ -2225,25 +1879,17 @@
           <t xml:space="preserve">    Short-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E70" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="71">
@@ -2252,25 +1898,17 @@
           <t xml:space="preserve">  Short-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E71" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="72">
@@ -2279,25 +1917,17 @@
           <t xml:space="preserve">    Current Deferred Revenue</t>
         </is>
       </c>
-      <c r="B72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E72" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="73">
@@ -2306,25 +1936,17 @@
           <t xml:space="preserve">    Current Deferred Taxes Liabilities</t>
         </is>
       </c>
-      <c r="B73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E73" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D73" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E73" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="74">
@@ -2333,25 +1955,17 @@
           <t xml:space="preserve">  Deferred Tax And Revenue</t>
         </is>
       </c>
-      <c r="B74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E74" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D74" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E74" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="75">
@@ -2360,25 +1974,17 @@
           <t xml:space="preserve">  Other Current Liabilities</t>
         </is>
       </c>
-      <c r="B75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E75" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D75" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E75" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="76">
@@ -2414,25 +2020,17 @@
           <t xml:space="preserve">    Long-Term Debt</t>
         </is>
       </c>
-      <c r="B77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E77" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D77" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E77" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="78">
@@ -2441,25 +2039,17 @@
           <t xml:space="preserve">    Long-Term Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E78" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D78" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E78" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="79">
@@ -2468,25 +2058,17 @@
           <t xml:space="preserve">  Long-Term Debt &amp; Capital Lease Obligation</t>
         </is>
       </c>
-      <c r="B79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E79" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D79" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E79" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="80">
@@ -2522,25 +2104,17 @@
           <t xml:space="preserve">  Pension And Retirement Benefit</t>
         </is>
       </c>
-      <c r="B81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E81" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D81" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E81" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="82">
@@ -2549,25 +2123,17 @@
           <t xml:space="preserve">    NonCurrent Deferred Revenue</t>
         </is>
       </c>
-      <c r="B82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E82" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D82" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E82" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="83">
@@ -2576,25 +2142,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Liabilities</t>
         </is>
       </c>
-      <c r="B83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E83" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D83" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E83" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="84">
@@ -2603,25 +2161,17 @@
           <t xml:space="preserve">  NonCurrent Deferred Income Tax</t>
         </is>
       </c>
-      <c r="B84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E84" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D84" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E84" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="85">
@@ -2630,25 +2180,17 @@
           <t xml:space="preserve">  Other Long-Term Liabilities</t>
         </is>
       </c>
-      <c r="B85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E85" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D85" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E85" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="86">
@@ -2703,25 +2245,17 @@
           <t xml:space="preserve">  Common Stock</t>
         </is>
       </c>
-      <c r="B88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E88" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B88" s="3" t="n">
+        <v>0.697588</v>
+      </c>
+      <c r="C88" s="3" t="n">
+        <v>0.697588</v>
+      </c>
+      <c r="D88" s="3" t="n">
+        <v>0.697588</v>
+      </c>
+      <c r="E88" s="3" t="n">
+        <v>0.697588</v>
       </c>
     </row>
     <row r="89">
@@ -2730,25 +2264,17 @@
           <t xml:space="preserve">  Preferred Stock</t>
         </is>
       </c>
-      <c r="B89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E89" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D89" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E89" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="90">
@@ -2776,25 +2302,17 @@
           <t xml:space="preserve">  Accumulated other comprehensive income (loss)</t>
         </is>
       </c>
-      <c r="B91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E91" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D91" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E91" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="92">
@@ -2803,25 +2321,17 @@
           <t xml:space="preserve">  Additional Paid-In Capital</t>
         </is>
       </c>
-      <c r="B92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E92" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D92" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E92" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="93">
@@ -2830,25 +2340,17 @@
           <t xml:space="preserve">  Treasury Stock</t>
         </is>
       </c>
-      <c r="B93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E93" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D93" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E93" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="94">
@@ -2857,25 +2359,17 @@
           <t xml:space="preserve">  Total Stockholders Equity</t>
         </is>
       </c>
-      <c r="B94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E94" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B94" s="3" t="n">
+        <v>0.603936</v>
+      </c>
+      <c r="C94" s="3" t="n">
+        <v>0.546463</v>
+      </c>
+      <c r="D94" s="3" t="n">
+        <v>0.500986</v>
+      </c>
+      <c r="E94" s="3" t="n">
+        <v>0.466899</v>
       </c>
     </row>
     <row r="95">
@@ -2884,25 +2378,17 @@
           <t xml:space="preserve">  Minority Interest</t>
         </is>
       </c>
-      <c r="B95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E95" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="D95" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E95" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="96">
@@ -2911,25 +2397,17 @@
           <t>Total Equity</t>
         </is>
       </c>
-      <c r="B96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E96" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B96" s="3" t="n">
+        <v>0.603936</v>
+      </c>
+      <c r="C96" s="3" t="n">
+        <v>0.546463</v>
+      </c>
+      <c r="D96" s="3" t="n">
+        <v>0.500986</v>
+      </c>
+      <c r="E96" s="3" t="n">
+        <v>0.466899</v>
       </c>
     </row>
     <row r="97">
@@ -2938,25 +2416,17 @@
           <t>Equity-to-Asset</t>
         </is>
       </c>
-      <c r="B97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="D97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E97" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B97" s="3" t="n">
+        <v>0.9651055016843195</v>
+      </c>
+      <c r="C97" s="3" t="n">
+        <v>0.9539256742956794</v>
+      </c>
+      <c r="D97" s="3" t="n">
+        <v>0.9339244003422621</v>
+      </c>
+      <c r="E97" s="3" t="n">
+        <v>0.9223935264391069</v>
       </c>
     </row>
     <row r="98">
@@ -2972,15 +2442,11 @@
           <t xml:space="preserve">  Net Income From Continuing Operations</t>
         </is>
       </c>
-      <c r="B99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B99" s="3" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="C99" s="3" t="n">
+        <v>-0.057473</v>
       </c>
       <c r="D99" s="1" t="inlineStr">
         <is>
@@ -2999,15 +2465,11 @@
           <t xml:space="preserve">  Cash Flow Depreciation, Depletion and Amortization</t>
         </is>
       </c>
-      <c r="B100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C100" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D100" s="1" t="inlineStr">
         <is>
@@ -3026,15 +2488,11 @@
           <t xml:space="preserve">    Change In Receivables</t>
         </is>
       </c>
-      <c r="B101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C101" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D101" s="1" t="inlineStr">
         <is>
@@ -3053,15 +2511,11 @@
           <t xml:space="preserve">    Change In Inventory</t>
         </is>
       </c>
-      <c r="B102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C102" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D102" s="1" t="inlineStr">
         <is>
@@ -3080,15 +2534,11 @@
           <t xml:space="preserve">    Change In Prepaid Assets</t>
         </is>
       </c>
-      <c r="B103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B103" s="3" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="C103" s="3" t="n">
+        <v>-0.001774</v>
       </c>
       <c r="D103" s="1" t="inlineStr">
         <is>
@@ -3107,15 +2557,11 @@
           <t xml:space="preserve">    Change In Payables And Accrued Expense</t>
         </is>
       </c>
-      <c r="B104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B104" s="3" t="n">
+        <v>0.011737</v>
+      </c>
+      <c r="C104" s="3" t="n">
+        <v>0.004558</v>
       </c>
       <c r="D104" s="1" t="inlineStr">
         <is>
@@ -3134,15 +2580,11 @@
           <t xml:space="preserve">    Change In Other Working Capital</t>
         </is>
       </c>
-      <c r="B105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C105" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D105" s="1" t="inlineStr">
         <is>
@@ -3161,15 +2603,11 @@
           <t xml:space="preserve">  Change In Working Capital</t>
         </is>
       </c>
-      <c r="B106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B106" s="3" t="n">
+        <v>0.010237</v>
+      </c>
+      <c r="C106" s="3" t="n">
+        <v>0.002784</v>
       </c>
       <c r="D106" s="1" t="inlineStr">
         <is>
@@ -3188,15 +2626,11 @@
           <t xml:space="preserve">  Stock Based Compensation</t>
         </is>
       </c>
-      <c r="B107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B107" s="3" t="n">
+        <v>0.071297</v>
+      </c>
+      <c r="C107" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D107" s="1" t="inlineStr">
         <is>
@@ -3215,15 +2649,11 @@
           <t xml:space="preserve">  Asset Impairment Charge</t>
         </is>
       </c>
-      <c r="B108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C108" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D108" s="1" t="inlineStr">
         <is>
@@ -3242,15 +2672,11 @@
           <t xml:space="preserve">  Cash from Discontinued Operating Activities</t>
         </is>
       </c>
-      <c r="B109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C109" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D109" s="1" t="inlineStr">
         <is>
@@ -3269,15 +2695,11 @@
           <t xml:space="preserve">  Cash Flow from Others</t>
         </is>
       </c>
-      <c r="B110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C110" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D110" s="1" t="inlineStr">
         <is>
@@ -3296,15 +2718,11 @@
           <t xml:space="preserve">  Purchase Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C111" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D111" s="1" t="inlineStr">
         <is>
@@ -3323,15 +2741,11 @@
           <t xml:space="preserve">  Sale Of Property, Plant, Equipment</t>
         </is>
       </c>
-      <c r="B112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C112" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D112" s="1" t="inlineStr">
         <is>
@@ -3350,15 +2764,11 @@
           <t xml:space="preserve">  Purchase Of Business</t>
         </is>
       </c>
-      <c r="B113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C113" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D113" s="1" t="inlineStr">
         <is>
@@ -3377,15 +2787,11 @@
           <t xml:space="preserve">  Purchase Of Investment</t>
         </is>
       </c>
-      <c r="B114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C114" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D114" s="1" t="inlineStr">
         <is>
@@ -3404,15 +2810,11 @@
           <t xml:space="preserve">  Sale Of Investment</t>
         </is>
       </c>
-      <c r="B115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C115" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D115" s="1" t="inlineStr">
         <is>
@@ -3431,15 +2833,11 @@
           <t xml:space="preserve">  Net Intangibles Purchase And Sale</t>
         </is>
       </c>
-      <c r="B116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C116" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D116" s="1" t="inlineStr">
         <is>
@@ -3458,15 +2856,11 @@
           <t xml:space="preserve">  Cash From Discontinued Investing Activities</t>
         </is>
       </c>
-      <c r="B117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C117" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D117" s="1" t="inlineStr">
         <is>
@@ -3485,15 +2879,11 @@
           <t xml:space="preserve">  Cash From Other Investing Activities</t>
         </is>
       </c>
-      <c r="B118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C118" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D118" s="1" t="inlineStr">
         <is>
@@ -3512,10 +2902,8 @@
           <t>Cash Flow from Investing</t>
         </is>
       </c>
-      <c r="B119" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B119" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="C119" s="1" t="inlineStr">
         <is>
@@ -3539,15 +2927,11 @@
           <t xml:space="preserve">  Issuance of Stock</t>
         </is>
       </c>
-      <c r="B120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C120" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D120" s="1" t="inlineStr">
         <is>
@@ -3566,15 +2950,11 @@
           <t xml:space="preserve">  Repurchase of Stock</t>
         </is>
       </c>
-      <c r="B121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C121" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D121" s="1" t="inlineStr">
         <is>
@@ -3593,15 +2973,11 @@
           <t xml:space="preserve">  Net Issuance of Preferred Stock</t>
         </is>
       </c>
-      <c r="B122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C122" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D122" s="1" t="inlineStr">
         <is>
@@ -3620,15 +2996,11 @@
           <t xml:space="preserve">    Issuance of Debt</t>
         </is>
       </c>
-      <c r="B123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C123" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D123" s="1" t="inlineStr">
         <is>
@@ -3647,15 +3019,11 @@
           <t xml:space="preserve">    Payments of Debt</t>
         </is>
       </c>
-      <c r="B124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C124" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D124" s="1" t="inlineStr">
         <is>
@@ -3674,15 +3042,11 @@
           <t xml:space="preserve">  Net Issuance of Debt</t>
         </is>
       </c>
-      <c r="B125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C125" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D125" s="1" t="inlineStr">
         <is>
@@ -3701,15 +3065,11 @@
           <t xml:space="preserve">  Cash Flow for Dividends</t>
         </is>
       </c>
-      <c r="B126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C126" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D126" s="1" t="inlineStr">
         <is>
@@ -3755,15 +3115,11 @@
           <t xml:space="preserve">  Other Financing</t>
         </is>
       </c>
-      <c r="B128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C128" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D128" s="1" t="inlineStr">
         <is>
@@ -3834,15 +3190,11 @@
           <t xml:space="preserve">    Effect of Exchange Rate Changes</t>
         </is>
       </c>
-      <c r="B131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C131" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D131" s="1" t="inlineStr">
         <is>
@@ -3911,15 +3263,11 @@
           <t>Capital Expenditure</t>
         </is>
       </c>
-      <c r="B134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="C134" s="3" t="n">
+        <v>0</v>
       </c>
       <c r="D134" s="1" t="inlineStr">
         <is>
@@ -3938,15 +3286,11 @@
           <t>Free Cash Flow</t>
         </is>
       </c>
-      <c r="B135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="C135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="B135" s="3" t="n">
+        <v>-0.116113</v>
+      </c>
+      <c r="C135" s="3" t="n">
+        <v>-0.049226</v>
       </c>
       <c r="D135" s="1" t="inlineStr">
         <is>
@@ -3970,7 +3314,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H72"/>
+  <dimension ref="A1:H71"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -4173,7 +3517,11 @@
           <t>Trade payables and accrued liabilities 5 $</t>
         </is>
       </c>
-      <c r="D6" t="inlineStr"/>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>CurrentAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E6" s="5" t="n">
         <v>0.021836</v>
       </c>
@@ -4335,7 +3683,11 @@
           <t>Shareholders’ Equity total</t>
         </is>
       </c>
-      <c r="D11" t="inlineStr"/>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>StockholdersEquity</t>
+        </is>
+      </c>
       <c r="E11" s="5" t="n">
         <v>0.603936</v>
       </c>
@@ -4467,7 +3819,11 @@
           <t>GST receivable</t>
         </is>
       </c>
-      <c r="D15" t="inlineStr"/>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>OtherReceivables</t>
+        </is>
+      </c>
       <c r="E15" s="5" t="n">
         <v>0.005463</v>
       </c>
@@ -4537,7 +3893,11 @@
           <t>Net loss $</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E17" s="5" t="n">
         <v>-0.192185</v>
       </c>
@@ -4571,7 +3931,11 @@
           <t>Share-based payments</t>
         </is>
       </c>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>StockBasedCompensation</t>
+        </is>
+      </c>
       <c r="E18" s="5" t="n">
         <v>0.071297</v>
       </c>
@@ -4641,7 +4005,11 @@
           <t>Prepaid expenses</t>
         </is>
       </c>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>ChangeInPrepaidAssets</t>
+        </is>
+      </c>
       <c r="E20" s="5" t="n">
         <v>-0.0015</v>
       </c>
@@ -4711,7 +4079,11 @@
           <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>ChangeInPayablesAndAccruedExpense</t>
+        </is>
+      </c>
       <c r="E22" s="5" t="n">
         <v>0.011737</v>
       </c>
@@ -5005,7 +4377,11 @@
           <t>Bank charges $ 354 $</t>
         </is>
       </c>
-      <c r="D30" t="inlineStr"/>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E30" t="inlineStr">
         <is>
           <t>-</t>
@@ -5041,7 +4417,11 @@
           <t>Filing and transfer agent fees 10,854</t>
         </is>
       </c>
-      <c r="D31" t="inlineStr"/>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E31" t="inlineStr">
         <is>
           <t>-</t>
@@ -5154,14 +4534,16 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>49,098</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Operating Expenses total</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>0.192184</v>
       </c>
       <c r="F34" s="5" t="n">
         <v>0.064777</v>
@@ -5193,7 +4575,11 @@
           <t>Foreign exchange loss (5)</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -5268,10 +4654,14 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>15,011</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr"/>
+          <t>Other Income (Expenses) total</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -5671,7 +5061,11 @@
           <t>Bank charges $</t>
         </is>
       </c>
-      <c r="D48" t="inlineStr"/>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E48" s="5" t="n">
         <v>0.000676</v>
       </c>
@@ -5741,7 +5135,11 @@
           <t>Filing and transfer agent fees</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.031509</v>
       </c>
@@ -5923,7 +5321,11 @@
           <t>Travel</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr"/>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E55" s="5" t="n">
         <v>0.000102</v>
       </c>
@@ -5949,20 +5351,24 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Operating Expenses total</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
-        <v>0.192184</v>
+        <v>-1e-06</v>
       </c>
       <c r="F56" s="5" t="n">
-        <v>0.05959</v>
+        <v>-1e-06</v>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -5988,15 +5394,21 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D57" t="inlineStr"/>
-      <c r="E57" s="5" t="n">
-        <v>-1e-06</v>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F57" s="5" t="n">
-        <v>-1e-06</v>
+        <v>0.002118</v>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -6022,21 +5434,19 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Other Expenses total</t>
         </is>
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
-        </is>
-      </c>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E58" s="5" t="n">
+        <v>-1e-06</v>
       </c>
       <c r="F58" s="5" t="n">
-        <v>0.002118</v>
+        <v>0.002117</v>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -6062,15 +5472,19 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Other Expenses total</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr"/>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E59" s="5" t="n">
-        <v>-1e-06</v>
+        <v>-0.192185</v>
       </c>
       <c r="F59" s="5" t="n">
-        <v>0.002117</v>
+        <v>-0.057473</v>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -6096,15 +5510,19 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E60" s="5" t="n">
-        <v>-0.192185</v>
+        <v>-3e-08</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-0.057473</v>
+        <v>-1e-08</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -6125,24 +5543,20 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Weighted average common shares outstanding –</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Weighted average common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>-3e-08</v>
+        <v>7.593413</v>
       </c>
       <c r="F61" s="5" t="n">
-        <v>-1e-08</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -6168,15 +5582,15 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding – basic and diluted</t>
+          <t>FOR THE YEAR ENDED MAY</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>7.593413</v>
+        <v>0.002023</v>
       </c>
       <c r="F62" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -6197,20 +5611,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding –</t>
+          <t>Number of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>FOR THE YEAR ENDED MAY</t>
+          <t>Balance at May 31, 2021 4,300,001 $ 285,001 $ - $</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.002023</v>
+        <v>0.274825</v>
       </c>
       <c r="F63" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>-0.010176</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -6236,15 +5650,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2021 4,300,001 $ 285,001 $ - $</t>
+          <t>Share issuance for cash 5,000,000 500,000 -</t>
         </is>
       </c>
       <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.274825</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>-0.010176</v>
+        <v>0.5</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -6270,12 +5686,12 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Share issuance for cash 5,000,000 500,000 -</t>
+          <t>Share issuance fees - (50,000) -</t>
         </is>
       </c>
       <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>0.5</v>
+        <v>-0.05</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
@@ -6306,12 +5722,12 @@
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Share issuance fees - (50,000) -</t>
+          <t>Issuance of stock options - - 71,297</t>
         </is>
       </c>
       <c r="D66" t="inlineStr"/>
       <c r="E66" s="5" t="n">
-        <v>-0.05</v>
+        <v>0.071297</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
@@ -6342,12 +5758,14 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Issuance of stock options - - 71,297</t>
+          <t>Issuance of agent’s options (37,412) 37,412</t>
         </is>
       </c>
       <c r="D67" t="inlineStr"/>
-      <c r="E67" s="5" t="n">
-        <v>0.071297</v>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
@@ -6378,14 +5796,12 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Issuance of agent’s options (37,412) 37,412</t>
+          <t>Repurchase and cancelation of incorporation share (1) (1) -</t>
         </is>
       </c>
       <c r="D68" t="inlineStr"/>
-      <c r="E68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E68" s="5" t="n">
+        <v>-1e-06</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
@@ -6416,17 +5832,19 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Repurchase and cancelation of incorporation share (1) (1) -</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr"/>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E69" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.192185</v>
+      </c>
+      <c r="F69" s="5" t="n">
+        <v>-0.192185</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -6452,19 +5870,15 @@
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Balance at May 31, 2022 9,300,000 697,588 108,709</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>-0.192185</v>
+        <v>0.603936</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.192185</v>
+        <v>-0.202361</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -6490,15 +5904,15 @@
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2022 9,300,000 697,588 108,709</t>
+          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
-        <v>0.603936</v>
+        <v>0.546463</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-0.202361</v>
+        <v>-0.259834</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -6506,40 +5920,6 @@
         </is>
       </c>
       <c r="H71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>income_statement</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
-        </is>
-      </c>
-      <c r="C72" t="inlineStr">
-        <is>
-          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
-      <c r="E72" s="5" t="n">
-        <v>0.546463</v>
-      </c>
-      <c r="F72" s="5" t="n">
-        <v>-0.259834</v>
-      </c>
-      <c r="G72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H72" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/DAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/DAQ.P.xlsx
@@ -431,6 +431,13 @@
   </sheetPr>
   <dimension ref="A1:E135"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="56" customWidth="1" min="1" max="1"/>
+    <col width="18" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="18" customWidth="1" min="5" max="5"/>
+  </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">

--- a/output/pdf_financials_xlsx/DAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/DAQ.P.xlsx
@@ -492,15 +492,11 @@
       <c r="C4" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E4" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D4" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="5">
@@ -515,15 +511,11 @@
       <c r="C5" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E5" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D5" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -538,15 +530,11 @@
       <c r="C6" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E6" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D6" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="7">
@@ -561,15 +549,11 @@
       <c r="C7" s="3" t="n">
         <v>0.012313</v>
       </c>
-      <c r="D7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E7" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D7" s="3" t="n">
+        <v>0.012313</v>
+      </c>
+      <c r="E7" s="3" t="n">
+        <v>0.011208</v>
       </c>
     </row>
     <row r="8">
@@ -584,15 +568,11 @@
       <c r="C8" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E8" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D8" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="9">
@@ -607,15 +587,11 @@
       <c r="C9" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E9" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D9" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="10">
@@ -630,15 +606,11 @@
       <c r="C10" s="3" t="n">
         <v>0.064777</v>
       </c>
-      <c r="D10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E10" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D10" s="3" t="n">
+        <v>0.064777</v>
+      </c>
+      <c r="E10" s="3" t="n">
+        <v>0.049098</v>
       </c>
     </row>
     <row r="11">
@@ -653,15 +625,11 @@
       <c r="C11" s="3" t="n">
         <v>-0.064777</v>
       </c>
-      <c r="D11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E11" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D11" s="3" t="n">
+        <v>-0.064777</v>
+      </c>
+      <c r="E11" s="3" t="n">
+        <v>-0.049098</v>
       </c>
     </row>
     <row r="12">
@@ -676,15 +644,11 @@
       <c r="C12" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E12" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D12" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="13">
@@ -694,20 +658,16 @@
         </is>
       </c>
       <c r="B13" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E13" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E13" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="14">
@@ -722,15 +682,11 @@
       <c r="C14" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E14" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D14" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="15">
@@ -745,15 +701,11 @@
       <c r="C15" s="3" t="n">
         <v>-1e-06</v>
       </c>
-      <c r="D15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E15" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D15" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="3" t="n">
+        <v>-5e-06</v>
       </c>
     </row>
     <row r="16">
@@ -768,15 +720,11 @@
       <c r="C16" s="3" t="n">
         <v>-0.192185</v>
       </c>
-      <c r="D16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E16" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D16" s="3" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="E16" s="3" t="n">
+        <v>-0.045477</v>
       </c>
     </row>
     <row r="17">
@@ -786,20 +734,16 @@
         </is>
       </c>
       <c r="B17" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="C17" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E17" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0</v>
+      </c>
+      <c r="D17" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E17" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="18">
@@ -868,15 +812,11 @@
       <c r="C20" s="3" t="n">
         <v>-0.192185</v>
       </c>
-      <c r="D20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E20" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D20" s="3" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="E20" s="3" t="n">
+        <v>-0.045477</v>
       </c>
     </row>
     <row r="21">
@@ -891,15 +831,11 @@
       <c r="C21" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E21" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D21" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -914,15 +850,11 @@
       <c r="C22" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E22" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D22" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -937,15 +869,11 @@
       <c r="C23" s="3" t="n">
         <v>-0.192185</v>
       </c>
-      <c r="D23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E23" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D23" s="3" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="E23" s="3" t="n">
+        <v>-0.045477</v>
       </c>
     </row>
     <row r="24">
@@ -960,15 +888,11 @@
       <c r="C24" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E24" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D24" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E24" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="25">
@@ -983,15 +907,11 @@
       <c r="C25" s="3" t="n">
         <v>-0.01</v>
       </c>
-      <c r="D25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E25" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D25" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -1031,15 +951,11 @@
       <c r="C27" s="3" t="n">
         <v>-0.192185</v>
       </c>
-      <c r="D27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E27" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D27" s="3" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="E27" s="3" t="n">
+        <v>-0.045477</v>
       </c>
     </row>
     <row r="28">
@@ -1054,15 +970,11 @@
       <c r="C28" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E28" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D28" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="29">
@@ -1077,15 +989,11 @@
       <c r="C29" s="3" t="n">
         <v>-0.192185</v>
       </c>
-      <c r="D29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E29" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D29" s="3" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="E29" s="3" t="n">
+        <v>-0.045477</v>
       </c>
     </row>
     <row r="30">
@@ -1127,15 +1035,11 @@
       <c r="C31" s="3" t="n">
         <v>-0</v>
       </c>
-      <c r="D31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E31" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D31" s="3" t="n">
+        <v>-0</v>
+      </c>
+      <c r="E31" s="3" t="n">
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -3321,7 +3225,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H71"/>
+  <dimension ref="A1:H79"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3858,7 +3762,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ended Ended</t>
+          <t>Ended                  Ended</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4555,15 +4459,11 @@
       <c r="F34" s="5" t="n">
         <v>0.064777</v>
       </c>
-      <c r="G34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H34" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G34" s="5" t="n">
+        <v>0.064777</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>0.049098</v>
       </c>
     </row>
     <row r="35">
@@ -4677,15 +4577,11 @@
       <c r="F37" s="5" t="n">
         <v>0.0193</v>
       </c>
-      <c r="G37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G37" s="5" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="H37" s="5" t="n">
+        <v>0.015011</v>
       </c>
     </row>
     <row r="38">
@@ -5026,30 +4922,30 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Ended Ended</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Note May 31, 2023 May</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr"/>
+          <t>Bank charges $</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E47" s="5" t="n">
-        <v>0.002022</v>
+        <v>0.000676</v>
       </c>
       <c r="F47" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H47" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000319</v>
+      </c>
+      <c r="G47" s="5" t="n">
+        <v>0.000346</v>
+      </c>
+      <c r="H47" s="5" t="n">
+        <v>0.000354</v>
       </c>
     </row>
     <row r="48">
@@ -5065,7 +4961,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Bank charges $</t>
+          <t>Filing and transfer agent fees</t>
         </is>
       </c>
       <c r="D48" t="inlineStr">
@@ -5074,20 +4970,16 @@
         </is>
       </c>
       <c r="E48" s="5" t="n">
-        <v>0.000676</v>
+        <v>0.031509</v>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.000319</v>
-      </c>
-      <c r="G48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H48" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.012164</v>
+      </c>
+      <c r="G48" s="5" t="n">
+        <v>0.011967</v>
+      </c>
+      <c r="H48" s="5" t="n">
+        <v>0.010854</v>
       </c>
     </row>
     <row r="49">
@@ -5103,27 +4995,25 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Corporate finance fees 6</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr"/>
+          <t>Office and administrative expenses</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
       <c r="E49" s="5" t="n">
-        <v>0.008</v>
-      </c>
-      <c r="F49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H49" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.013624</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>0.020362</v>
+      </c>
+      <c r="G49" s="5" t="n">
+        <v>0.024383</v>
+      </c>
+      <c r="H49" s="5" t="n">
+        <v>0.020761</v>
       </c>
     </row>
     <row r="50">
@@ -5139,29 +5029,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Filing and transfer agent fees</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.031509</v>
+        <v>0.061918</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.012164</v>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.02507</v>
+      </c>
+      <c r="G50" s="5" t="n">
+        <v>0.028081</v>
+      </c>
+      <c r="H50" s="5" t="n">
+        <v>0.017129</v>
       </c>
     </row>
     <row r="51">
@@ -5172,17 +5058,23 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Marketing and investor relations expenses</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr"/>
-      <c r="E51" s="5" t="n">
-        <v>0.005058</v>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
@@ -5194,10 +5086,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H51" s="5" t="n">
+        <v>-5e-06</v>
       </c>
     </row>
     <row r="52">
@@ -5208,34 +5098,34 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Office and administrative expenses</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E52" s="5" t="n">
-        <v>0.013624</v>
-      </c>
-      <c r="F52" s="5" t="n">
-        <v>0.020362</v>
-      </c>
-      <c r="G52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G52" s="5" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="H52" s="5" t="n">
+        <v>0.015016</v>
       </c>
     </row>
     <row r="53">
@@ -5246,34 +5136,34 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Net and comprehensive loss $</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
-        </is>
-      </c>
-      <c r="E53" s="5" t="n">
-        <v>0.061918</v>
-      </c>
-      <c r="F53" s="5" t="n">
-        <v>0.02507</v>
-      </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G53" s="5" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="H53" s="5" t="n">
+        <v>-0.034087</v>
       </c>
     </row>
     <row r="54">
@@ -5284,32 +5174,34 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Share-based payments 6, 7</t>
-        </is>
-      </c>
-      <c r="D54" t="inlineStr"/>
-      <c r="E54" s="5" t="n">
-        <v>0.071297</v>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
+      <c r="E54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H54" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G54" s="5" t="n">
+        <v>0</v>
+      </c>
+      <c r="H54" s="5" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="55">
@@ -5320,34 +5212,26 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Weighted average common shares outstanding –</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Weighted average common shares outstanding – basic and diluted</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
       <c r="E55" s="5" t="n">
-        <v>0.000102</v>
+        <v>7.593413</v>
       </c>
       <c r="F55" s="5" t="n">
-        <v>0.001675</v>
-      </c>
-      <c r="G55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>9.300000000000001</v>
+      </c>
+      <c r="G55" s="5" t="n">
+        <v>9.300000000000001</v>
+      </c>
+      <c r="H55" s="5" t="n">
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="56">
@@ -5358,34 +5242,30 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E56" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="F56" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="G56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G56" s="5" t="n">
+        <v>0.546463</v>
+      </c>
+      <c r="H56" s="5" t="n">
+        <v>-0.259834</v>
       </c>
     </row>
     <row r="57">
@@ -5396,17 +5276,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Net loss - - -</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>NetIncome</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5414,18 +5294,16 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F57" s="5" t="n">
-        <v>0.002118</v>
-      </c>
-      <c r="G57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H57" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G57" s="5" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="H57" s="5" t="n">
+        <v>-0.045477</v>
       </c>
     </row>
     <row r="58">
@@ -5436,34 +5314,30 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Other Expenses total</t>
-        </is>
-      </c>
-      <c r="D58" t="inlineStr">
-        <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E58" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="F58" s="5" t="n">
-        <v>0.002117</v>
-      </c>
-      <c r="G58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance at May 31, 2024 9,300,000 $ 697,588 $ 108,709 $</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G58" s="5" t="n">
+        <v>0.500986</v>
+      </c>
+      <c r="H58" s="5" t="n">
+        <v>-0.305311</v>
       </c>
     </row>
     <row r="59">
@@ -5474,34 +5348,30 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
-        </is>
-      </c>
-      <c r="D59" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E59" s="5" t="n">
-        <v>-0.192185</v>
-      </c>
-      <c r="F59" s="5" t="n">
-        <v>-0.057473</v>
-      </c>
-      <c r="G59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Balance at May 31, 2025 9,300,000 $ 697,588 $ 108,709 $</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G59" s="5" t="n">
+        <v>0.466899</v>
+      </c>
+      <c r="H59" s="5" t="n">
+        <v>-0.339398</v>
       </c>
     </row>
     <row r="60">
@@ -5512,24 +5382,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Ended                 Ended</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr">
-        <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
+          <t>Note May 31, 2023 May</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
       <c r="E60" s="5" t="n">
-        <v>-3e-08</v>
+        <v>0.002022</v>
       </c>
       <c r="F60" s="5" t="n">
-        <v>-1e-08</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -5550,20 +5416,22 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding –</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding – basic and diluted</t>
+          <t>Corporate finance fees 6</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
       <c r="E61" s="5" t="n">
-        <v>7.593413</v>
-      </c>
-      <c r="F61" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>0.008</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -5584,20 +5452,22 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding –</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>FOR THE YEAR ENDED MAY</t>
+          <t>Marketing and investor relations expenses</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
       <c r="E62" s="5" t="n">
-        <v>0.002023</v>
-      </c>
-      <c r="F62" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.005058</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -5618,20 +5488,22 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2021 4,300,001 $ 285,001 $ - $</t>
+          <t>Share-based payments 6, 7</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.274825</v>
-      </c>
-      <c r="F63" s="5" t="n">
-        <v>-0.010176</v>
+        <v>0.071297</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -5652,22 +5524,24 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Share issuance for cash 5,000,000 500,000 -</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr"/>
+          <t>Travel</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E64" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F64" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.000102</v>
+      </c>
+      <c r="F64" s="5" t="n">
+        <v>0.001675</v>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5688,22 +5562,24 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Share issuance fees - (50,000) -</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr"/>
+          <t>Foreign exchange loss</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E65" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-1e-06</v>
+      </c>
+      <c r="F65" s="5" t="n">
+        <v>-1e-06</v>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5724,22 +5600,26 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Issuance of stock options - - 71,297</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr"/>
-      <c r="E66" s="5" t="n">
-        <v>0.071297</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>InterestIncome</t>
+        </is>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F66" s="5" t="n">
+        <v>0.002118</v>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5760,24 +5640,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Issuance of agent’s options (37,412) 37,412</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr"/>
-      <c r="E67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Other Expenses total</t>
+        </is>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>1e-06</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>0.002117</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5798,22 +5678,24 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Repurchase and cancelation of incorporation share (1) (1) -</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr"/>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E68" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.192185</v>
+      </c>
+      <c r="F68" s="5" t="n">
+        <v>-0.057473</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5834,24 +5716,24 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E69" s="5" t="n">
-        <v>-0.192185</v>
+        <v>-3e-08</v>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-0.192185</v>
+        <v>-1e-08</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5872,20 +5754,20 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Weighted average common shares outstanding –</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2022 9,300,000 697,588 108,709</t>
+          <t>FOR THE YEAR ENDED MAY</t>
         </is>
       </c>
       <c r="D70" t="inlineStr"/>
       <c r="E70" s="5" t="n">
-        <v>0.603936</v>
+        <v>0.002023</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>-0.202361</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5906,27 +5788,315 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
+          <t>Balance at May 31, 2021 4,300,001 $ 285,001 $ - $</t>
         </is>
       </c>
       <c r="D71" t="inlineStr"/>
       <c r="E71" s="5" t="n">
+        <v>0.274825</v>
+      </c>
+      <c r="F71" s="5" t="n">
+        <v>-0.010176</v>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Share issuance for cash 5,000,000 500,000 -</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr"/>
+      <c r="E72" s="5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Share issuance fees - (50,000) -</t>
+        </is>
+      </c>
+      <c r="D73" t="inlineStr"/>
+      <c r="E73" s="5" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Issuance of stock options - - 71,297</t>
+        </is>
+      </c>
+      <c r="D74" t="inlineStr"/>
+      <c r="E74" s="5" t="n">
+        <v>0.071297</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Issuance of agent’s options (37,412) 37,412</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr"/>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Repurchase and cancelation of incorporation share (1) (1) -</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr"/>
+      <c r="E76" s="5" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E77" s="5" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="F77" s="5" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Balance at May 31, 2022 9,300,000 697,588 108,709</t>
+        </is>
+      </c>
+      <c r="D78" t="inlineStr"/>
+      <c r="E78" s="5" t="n">
+        <v>0.603936</v>
+      </c>
+      <c r="F78" s="5" t="n">
+        <v>-0.202361</v>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
+        </is>
+      </c>
+      <c r="D79" t="inlineStr"/>
+      <c r="E79" s="5" t="n">
         <v>0.546463</v>
       </c>
-      <c r="F71" s="5" t="n">
+      <c r="F79" s="5" t="n">
         <v>-0.259834</v>
       </c>
-      <c r="G71" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
         <is>
           <t>-</t>
         </is>

--- a/output/pdf_financials_xlsx/DAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/DAQ.P.xlsx
@@ -2233,16 +2233,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>0.108709</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>0.108709</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.108709</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>0.108709</v>
       </c>
     </row>
     <row r="93">
@@ -3530,7 +3530,11 @@
           <t>Reserves 6</t>
         </is>
       </c>
-      <c r="D9" t="inlineStr"/>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E9" s="5" t="n">
         <v>0.108709</v>
       </c>

--- a/output/pdf_financials_xlsx/DAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/DAQ.P.xlsx
@@ -642,13 +642,13 @@
         <v>0</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>0</v>
+        <v>0.0193</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>0</v>
+        <v>0.0193</v>
       </c>
       <c r="E12" s="3" t="n">
-        <v>0</v>
+        <v>0.015016</v>
       </c>
     </row>
     <row r="13">
@@ -949,13 +949,13 @@
         <v>-0.192185</v>
       </c>
       <c r="C27" s="3" t="n">
-        <v>-0.192185</v>
+        <v>-0.211485</v>
       </c>
       <c r="D27" s="3" t="n">
-        <v>-0.045477</v>
+        <v>-0.064777</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>-0.045477</v>
+        <v>-0.060493</v>
       </c>
     </row>
     <row r="28">
@@ -987,13 +987,13 @@
         <v>-0.192185</v>
       </c>
       <c r="C29" s="3" t="n">
-        <v>-0.192185</v>
+        <v>-0.211485</v>
       </c>
       <c r="D29" s="3" t="n">
-        <v>-0.045477</v>
+        <v>-0.064777</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>-0.045477</v>
+        <v>-0.060493</v>
       </c>
     </row>
     <row r="30">
@@ -1083,16 +1083,16 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.6188090000000001</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.569583</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.533199</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.502007</v>
       </c>
     </row>
     <row r="35">
@@ -1121,16 +1121,16 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.6188090000000001</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.569583</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.533199</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.502007</v>
       </c>
     </row>
     <row r="37">
@@ -3324,7 +3324,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -3698,7 +3698,7 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E14" s="5" t="n">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -5112,7 +5112,7 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E52" t="inlineStr">
@@ -5614,7 +5614,7 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E66" t="inlineStr">

--- a/output/pdf_financials_xlsx/DAQ.P.xlsx
+++ b/output/pdf_financials_xlsx/DAQ.P.xlsx
@@ -2359,15 +2359,11 @@
       <c r="C99" s="3" t="n">
         <v>-0.057473</v>
       </c>
-      <c r="D99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E99" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D99" s="3" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="E99" s="3" t="n">
+        <v>-0.034087</v>
       </c>
     </row>
     <row r="100">
@@ -2382,15 +2378,11 @@
       <c r="C100" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E100" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D100" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E100" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="101">
@@ -2400,20 +2392,16 @@
         </is>
       </c>
       <c r="B101" s="3" t="n">
-        <v>0</v>
+        <v>-0.005463</v>
       </c>
       <c r="C101" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="D101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E101" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.005463</v>
+      </c>
+      <c r="D101" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E101" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="102">
@@ -2428,15 +2416,11 @@
       <c r="C102" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E102" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D102" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E102" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="103">
@@ -2451,15 +2435,11 @@
       <c r="C103" s="3" t="n">
         <v>-0.001774</v>
       </c>
-      <c r="D103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E103" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D103" s="3" t="n">
+        <v>4.2e-05</v>
+      </c>
+      <c r="E103" s="3" t="n">
+        <v>-0.000943</v>
       </c>
     </row>
     <row r="104">
@@ -2474,15 +2454,11 @@
       <c r="C104" s="3" t="n">
         <v>0.004558</v>
       </c>
-      <c r="D104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E104" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D104" s="3" t="n">
+        <v>0.009051</v>
+      </c>
+      <c r="E104" s="3" t="n">
+        <v>0.003838</v>
       </c>
     </row>
     <row r="105">
@@ -2497,15 +2473,11 @@
       <c r="C105" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E105" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D105" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E105" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="106">
@@ -2515,20 +2487,16 @@
         </is>
       </c>
       <c r="B106" s="3" t="n">
-        <v>0.010237</v>
+        <v>0.004774</v>
       </c>
       <c r="C106" s="3" t="n">
-        <v>0.002784</v>
-      </c>
-      <c r="D106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E106" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.008247000000000001</v>
+      </c>
+      <c r="D106" s="3" t="n">
+        <v>0.009093</v>
+      </c>
+      <c r="E106" s="3" t="n">
+        <v>0.002895</v>
       </c>
     </row>
     <row r="107">
@@ -2543,15 +2511,11 @@
       <c r="C107" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E107" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D107" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E107" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="108">
@@ -2566,15 +2530,11 @@
       <c r="C108" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E108" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D108" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E108" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="109">
@@ -2589,15 +2549,11 @@
       <c r="C109" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E109" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D109" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E109" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="110">
@@ -2612,15 +2568,11 @@
       <c r="C110" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E110" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D110" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E110" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="111">
@@ -2635,15 +2587,11 @@
       <c r="C111" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E111" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D111" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E111" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="112">
@@ -2658,15 +2606,11 @@
       <c r="C112" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E112" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D112" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E112" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="113">
@@ -2681,15 +2625,11 @@
       <c r="C113" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E113" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D113" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E113" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="114">
@@ -2704,15 +2644,11 @@
       <c r="C114" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E114" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D114" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E114" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="115">
@@ -2727,15 +2663,11 @@
       <c r="C115" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E115" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D115" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E115" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="116">
@@ -2750,15 +2682,11 @@
       <c r="C116" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E116" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D116" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E116" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="117">
@@ -2773,15 +2701,11 @@
       <c r="C117" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E117" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D117" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E117" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="118">
@@ -2796,15 +2720,11 @@
       <c r="C118" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E118" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D118" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E118" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="119">
@@ -2844,15 +2764,11 @@
       <c r="C120" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E120" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D120" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E120" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="121">
@@ -2867,15 +2783,11 @@
       <c r="C121" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E121" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D121" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E121" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="122">
@@ -2890,15 +2802,11 @@
       <c r="C122" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E122" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D122" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E122" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="123">
@@ -2913,15 +2821,11 @@
       <c r="C123" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E123" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D123" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E123" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="124">
@@ -2936,15 +2840,11 @@
       <c r="C124" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E124" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D124" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E124" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="125">
@@ -2959,15 +2859,11 @@
       <c r="C125" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E125" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D125" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E125" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="126">
@@ -2982,15 +2878,11 @@
       <c r="C126" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E126" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D126" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E126" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="127">
@@ -3032,15 +2924,11 @@
       <c r="C128" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E128" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D128" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E128" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="129">
@@ -3107,15 +2995,11 @@
       <c r="C131" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E131" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D131" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E131" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="132">
@@ -3130,15 +3014,11 @@
       <c r="C132" s="3" t="n">
         <v>-0.049226</v>
       </c>
-      <c r="D132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E132" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D132" s="3" t="n">
+        <v>-0.036384</v>
+      </c>
+      <c r="E132" s="3" t="n">
+        <v>-0.031192</v>
       </c>
     </row>
     <row r="133">
@@ -3180,15 +3060,11 @@
       <c r="C134" s="3" t="n">
         <v>0</v>
       </c>
-      <c r="D134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E134" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D134" s="3" t="n">
+        <v>0</v>
+      </c>
+      <c r="E134" s="3" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="135">
@@ -3203,15 +3079,11 @@
       <c r="C135" s="3" t="n">
         <v>-0.049226</v>
       </c>
-      <c r="D135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="E135" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="D135" s="3" t="n">
+        <v>-0.036384</v>
+      </c>
+      <c r="E135" s="3" t="n">
+        <v>-0.031192</v>
       </c>
     </row>
   </sheetData>
@@ -3225,7 +3097,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H79"/>
+  <dimension ref="A1:H82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -3766,30 +3638,30 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Ended                  Ended</t>
+          <t>Operating Activities</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>May 31, 2023 May</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr"/>
+          <t>Net loss $</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NetIncomeFromContinuingOperations</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
-        <v>0.002022</v>
+        <v>-0.192185</v>
       </c>
       <c r="F16" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.057473</v>
+      </c>
+      <c r="G16" s="5" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="H16" s="5" t="n">
+        <v>-0.034087</v>
       </c>
     </row>
     <row r="17">
@@ -3800,34 +3672,30 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Operating Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Net loss $</t>
+          <t>Prepaid expenses</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NetIncomeFromContinuingOperations</t>
+          <t>ChangeInPrepaidAssets</t>
         </is>
       </c>
       <c r="E17" s="5" t="n">
-        <v>-0.192185</v>
+        <v>-0.0015</v>
       </c>
       <c r="F17" s="5" t="n">
-        <v>-0.057473</v>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.001774</v>
+      </c>
+      <c r="G17" s="5" t="n">
+        <v>4.2e-05</v>
+      </c>
+      <c r="H17" s="5" t="n">
+        <v>-0.000943</v>
       </c>
     </row>
     <row r="18">
@@ -3838,36 +3706,30 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Items not affecting cash from operations</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Share-based payments</t>
+          <t>Trade payables and accrued liabilities</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>StockBasedCompensation</t>
+          <t>ChangeInPayablesAndAccruedExpense</t>
         </is>
       </c>
       <c r="E18" s="5" t="n">
-        <v>0.071297</v>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.011737</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>0.004558</v>
+      </c>
+      <c r="G18" s="5" t="n">
+        <v>0.009051</v>
+      </c>
+      <c r="H18" s="5" t="n">
+        <v>0.003838</v>
       </c>
     </row>
     <row r="19">
@@ -3883,25 +3745,25 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>GST receivable</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr"/>
+          <t>Cash flows used in operating activities</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>OperatingCashFlow</t>
+        </is>
+      </c>
       <c r="E19" s="5" t="n">
-        <v>-0.005463</v>
+        <v>-0.116113</v>
       </c>
       <c r="F19" s="5" t="n">
-        <v>0.005463</v>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.049226</v>
+      </c>
+      <c r="G19" s="5" t="n">
+        <v>-0.036384</v>
+      </c>
+      <c r="H19" s="5" t="n">
+        <v>-0.031192</v>
       </c>
     </row>
     <row r="20">
@@ -3917,29 +3779,29 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Prepaid expenses</t>
+          <t>Net Change in Cash</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>ChangeInPrepaidAssets</t>
-        </is>
-      </c>
-      <c r="E20" s="5" t="n">
-        <v>-0.0015</v>
-      </c>
-      <c r="F20" s="5" t="n">
-        <v>-0.001774</v>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G20" s="5" t="n">
+        <v>-0.036384</v>
+      </c>
+      <c r="H20" s="5" t="n">
+        <v>-0.031192</v>
       </c>
     </row>
     <row r="21">
@@ -3955,27 +3817,25 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Receivable from related parties</t>
+          <t>Cash – Beginning</t>
         </is>
       </c>
       <c r="D21" t="inlineStr"/>
-      <c r="E21" s="5" t="n">
-        <v>1e-06</v>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G21" s="5" t="n">
+        <v>0.569583</v>
+      </c>
+      <c r="H21" s="5" t="n">
+        <v>0.533199</v>
       </c>
     </row>
     <row r="22">
@@ -3991,29 +3851,25 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Trade payables and accrued liabilities</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>ChangeInPayablesAndAccruedExpense</t>
-        </is>
-      </c>
-      <c r="E22" s="5" t="n">
-        <v>0.011737</v>
-      </c>
-      <c r="F22" s="5" t="n">
-        <v>0.004558</v>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash – Ending $</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G22" s="5" t="n">
+        <v>0.533199</v>
+      </c>
+      <c r="H22" s="5" t="n">
+        <v>0.502007</v>
       </c>
     </row>
     <row r="23">
@@ -4024,24 +3880,20 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Changes in non-cash working capital items</t>
+          <t>Ended                  Ended</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Cash flows used in operating activities</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>OperatingCashFlow</t>
-        </is>
-      </c>
+          <t>May 31, 2023 May</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
       <c r="E23" s="5" t="n">
-        <v>-0.116113</v>
+        <v>0.002022</v>
       </c>
       <c r="F23" s="5" t="n">
-        <v>-0.049226</v>
+        <v>3.1e-05</v>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -4062,21 +3914,21 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Items not affecting cash from operations</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Issuance of shares, net</t>
+          <t>Share-based payments</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>CommonStockIssuance</t>
+          <t>StockBasedCompensation</t>
         </is>
       </c>
       <c r="E24" s="5" t="n">
-        <v>0.45</v>
+        <v>0.071297</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -4102,22 +3954,24 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Repurchase of incorporation share</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr"/>
+          <t>GST receivable</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>ChangeInReceivables</t>
+        </is>
+      </c>
       <c r="E25" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-0.005463</v>
+      </c>
+      <c r="F25" s="5" t="n">
+        <v>0.005463</v>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -4138,21 +3992,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Financing Activities</t>
+          <t>Changes in non-cash working capital items</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Cash Flows used in financing activities</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>FinancingCashFlow</t>
-        </is>
-      </c>
+          <t>Receivable from related parties</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
       <c r="E26" s="5" t="n">
-        <v>0.449999</v>
+        <v>1e-06</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -4183,19 +4033,21 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Net Change in Cash</t>
+          <t>Issuance of shares, net</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>ChangesInCash</t>
+          <t>CommonStockIssuance</t>
         </is>
       </c>
       <c r="E27" s="5" t="n">
-        <v>0.333886</v>
-      </c>
-      <c r="F27" s="5" t="n">
-        <v>-0.049226</v>
+        <v>0.45</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -4221,15 +4073,17 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Cash – Beginning</t>
+          <t>Repurchase of incorporation share</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
       <c r="E28" s="5" t="n">
-        <v>0.284923</v>
-      </c>
-      <c r="F28" s="5" t="n">
-        <v>0.6188090000000001</v>
+        <v>-1e-06</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -4255,15 +4109,21 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Cash – Ending $</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr"/>
+          <t>Cash Flows used in financing activities</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>FinancingCashFlow</t>
+        </is>
+      </c>
       <c r="E29" s="5" t="n">
-        <v>0.6188090000000001</v>
-      </c>
-      <c r="F29" s="5" t="n">
-        <v>0.569583</v>
+        <v>0.449999</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -4279,31 +4139,29 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bank charges $ 354 $</t>
+          <t>Net Change in Cash</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ChangesInCash</t>
+        </is>
+      </c>
+      <c r="E30" s="5" t="n">
+        <v>0.333886</v>
       </c>
       <c r="F30" s="5" t="n">
-        <v>0.000346</v>
+        <v>-0.049226</v>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -4319,31 +4177,25 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Filing and transfer agent fees 10,854</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash – Beginning</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" s="5" t="n">
+        <v>0.284923</v>
       </c>
       <c r="F31" s="5" t="n">
-        <v>0.011967</v>
+        <v>0.6188090000000001</v>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -4359,31 +4211,25 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>income_statement</t>
+          <t>cash_flow</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Financing Activities</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Office and administrative expenses 20,761</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E32" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Cash – Ending $</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" s="5" t="n">
+        <v>0.6188090000000001</v>
       </c>
       <c r="F32" s="5" t="n">
-        <v>0.024383</v>
+        <v>0.569583</v>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -4409,12 +4255,12 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Professional fees 17,129</t>
+          <t>Bank charges $ 354 $</t>
         </is>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -4423,7 +4269,7 @@
         </is>
       </c>
       <c r="F33" s="5" t="n">
-        <v>0.028081</v>
+        <v>0.000346</v>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -4449,25 +4295,31 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Operating Expenses total</t>
+          <t>Filing and transfer agent fees 10,854</t>
         </is>
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
-        </is>
-      </c>
-      <c r="E34" s="5" t="n">
-        <v>0.192184</v>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F34" s="5" t="n">
-        <v>0.064777</v>
-      </c>
-      <c r="G34" s="5" t="n">
-        <v>0.064777</v>
-      </c>
-      <c r="H34" s="5" t="n">
-        <v>0.049098</v>
+        <v>0.011967</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="35">
@@ -4478,17 +4330,17 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Foreign exchange loss (5)</t>
+          <t>Office and administrative expenses 20,761</t>
         </is>
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
+          <t>GeneralAndAdministrativeExpense</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
@@ -4496,10 +4348,8 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F35" s="5" t="n">
+        <v>0.024383</v>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -4520,17 +4370,17 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Interest income 15,016</t>
+          <t>Professional fees 17,129</t>
         </is>
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
@@ -4539,7 +4389,7 @@
         </is>
       </c>
       <c r="F36" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.028081</v>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -4560,12 +4410,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Other Income (Expenses) total</t>
+          <t>Operating Expenses total</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -4573,19 +4423,17 @@
           <t>OperatingExpense</t>
         </is>
       </c>
-      <c r="E37" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E37" s="5" t="n">
+        <v>0.192184</v>
       </c>
       <c r="F37" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.064777</v>
       </c>
       <c r="G37" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.064777</v>
       </c>
       <c r="H37" s="5" t="n">
-        <v>0.015011</v>
+        <v>0.049098</v>
       </c>
     </row>
     <row r="38">
@@ -4601,17 +4449,23 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $ (34,087) $</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr"/>
+          <t>Foreign exchange loss (5)</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>OtherIncomeExpense</t>
+        </is>
+      </c>
       <c r="E38" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F38" s="5" t="n">
-        <v>-0.045477</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -4637,17 +4491,21 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $ (0.00) $</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr"/>
+          <t>Interest income 15,016</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
       <c r="E39" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
       <c r="F39" s="5" t="n">
-        <v>0</v>
+        <v>0.0193</v>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -4673,12 +4531,12 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding</t>
+          <t>Other Income (Expenses) total</t>
         </is>
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>SharesOutstanding</t>
+          <t>OperatingExpense</t>
         </is>
       </c>
       <c r="E40" t="inlineStr">
@@ -4686,20 +4544,14 @@
           <t>-</t>
         </is>
       </c>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H40" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="F40" s="5" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="G40" s="5" t="n">
+        <v>0.0193</v>
+      </c>
+      <c r="H40" s="5" t="n">
+        <v>0.015011</v>
       </c>
     </row>
     <row r="41">
@@ -4715,7 +4567,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>basic and diluted 9,300,000</t>
+          <t>Net and comprehensive loss $ (34,087) $</t>
         </is>
       </c>
       <c r="D41" t="inlineStr"/>
@@ -4725,7 +4577,7 @@
         </is>
       </c>
       <c r="F41" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>-0.045477</v>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -4746,12 +4598,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $ (259,834) $</t>
+          <t>Loss per share – basic and diluted $ (0.00) $</t>
         </is>
       </c>
       <c r="D42" t="inlineStr"/>
@@ -4761,7 +4613,7 @@
         </is>
       </c>
       <c r="F42" s="5" t="n">
-        <v>0.546463</v>
+        <v>0</v>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -4782,22 +4634,28 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Net loss - - - (45,477)</t>
-        </is>
-      </c>
-      <c r="D43" t="inlineStr"/>
+          <t>Weighted average common shares outstanding</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>SharesOutstanding</t>
+        </is>
+      </c>
       <c r="E43" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="F43" s="5" t="n">
-        <v>-0.045477</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -4818,12 +4676,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Number of shares Amount Reserves Deficit Total</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2024 9,300,000 $ 697,588 $ 108,709 $ (305,311) $</t>
+          <t>basic and diluted 9,300,000</t>
         </is>
       </c>
       <c r="D44" t="inlineStr"/>
@@ -4833,7 +4691,7 @@
         </is>
       </c>
       <c r="F44" s="5" t="n">
-        <v>0.500986</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -4859,7 +4717,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Net loss - - - (34,087)</t>
+          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $ (259,834) $</t>
         </is>
       </c>
       <c r="D45" t="inlineStr"/>
@@ -4869,7 +4727,7 @@
         </is>
       </c>
       <c r="F45" s="5" t="n">
-        <v>-0.034087</v>
+        <v>0.546463</v>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -4895,7 +4753,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2025 9,300,000 $ 697,588 $ 108,709 $ (339,398) $</t>
+          <t>Net loss - - - (45,477)</t>
         </is>
       </c>
       <c r="D46" t="inlineStr"/>
@@ -4905,7 +4763,7 @@
         </is>
       </c>
       <c r="F46" s="5" t="n">
-        <v>0.466899</v>
+        <v>-0.045477</v>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -4926,30 +4784,32 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bank charges $</t>
-        </is>
-      </c>
-      <c r="D47" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E47" s="5" t="n">
-        <v>0.000676</v>
+          <t>Balance at May 31, 2024 9,300,000 $ 697,588 $ 108,709 $ (305,311) $</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F47" s="5" t="n">
-        <v>0.000319</v>
-      </c>
-      <c r="G47" s="5" t="n">
-        <v>0.000346</v>
-      </c>
-      <c r="H47" s="5" t="n">
-        <v>0.000354</v>
+        <v>0.500986</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="48">
@@ -4960,30 +4820,32 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Filing and transfer agent fees</t>
-        </is>
-      </c>
-      <c r="D48" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
-      <c r="E48" s="5" t="n">
-        <v>0.031509</v>
+          <t>Net loss - - - (34,087)</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F48" s="5" t="n">
-        <v>0.012164</v>
-      </c>
-      <c r="G48" s="5" t="n">
-        <v>0.011967</v>
-      </c>
-      <c r="H48" s="5" t="n">
-        <v>0.010854</v>
+        <v>-0.034087</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="49">
@@ -4994,30 +4856,32 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number of shares Amount Reserves Deficit Total</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Office and administrative expenses</t>
-        </is>
-      </c>
-      <c r="D49" t="inlineStr">
-        <is>
-          <t>GeneralAndAdministrativeExpense</t>
-        </is>
-      </c>
-      <c r="E49" s="5" t="n">
-        <v>0.013624</v>
+          <t>Balance at May 31, 2025 9,300,000 $ 697,588 $ 108,709 $ (339,398) $</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F49" s="5" t="n">
-        <v>0.020362</v>
-      </c>
-      <c r="G49" s="5" t="n">
-        <v>0.024383</v>
-      </c>
-      <c r="H49" s="5" t="n">
-        <v>0.020761</v>
+        <v>0.466899</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
     </row>
     <row r="50">
@@ -5033,25 +4897,25 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Professional fees</t>
+          <t>Bank charges $</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>ProfessionalExpenseAndContractServicesExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E50" s="5" t="n">
-        <v>0.061918</v>
+        <v>0.000676</v>
       </c>
       <c r="F50" s="5" t="n">
-        <v>0.02507</v>
+        <v>0.000319</v>
       </c>
       <c r="G50" s="5" t="n">
-        <v>0.028081</v>
+        <v>0.000346</v>
       </c>
       <c r="H50" s="5" t="n">
-        <v>0.017129</v>
+        <v>0.000354</v>
       </c>
     </row>
     <row r="51">
@@ -5062,36 +4926,30 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
+          <t>Filing and transfer agent fees</t>
         </is>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
+      <c r="E51" s="5" t="n">
+        <v>0.031509</v>
+      </c>
+      <c r="F51" s="5" t="n">
+        <v>0.012164</v>
+      </c>
+      <c r="G51" s="5" t="n">
+        <v>0.011967</v>
       </c>
       <c r="H51" s="5" t="n">
-        <v>-5e-06</v>
+        <v>0.010854</v>
       </c>
     </row>
     <row r="52">
@@ -5102,34 +4960,30 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Interest income</t>
+          <t>Office and administrative expenses</t>
         </is>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F52" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>GeneralAndAdministrativeExpense</t>
+        </is>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>0.013624</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>0.020362</v>
       </c>
       <c r="G52" s="5" t="n">
-        <v>0.0193</v>
+        <v>0.024383</v>
       </c>
       <c r="H52" s="5" t="n">
-        <v>0.015016</v>
+        <v>0.020761</v>
       </c>
     </row>
     <row r="53">
@@ -5140,34 +4994,30 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Other Income (Expenses)</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
+          <t>Professional fees</t>
         </is>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
-      <c r="E53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F53" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>ProfessionalExpenseAndContractServicesExpense</t>
+        </is>
+      </c>
+      <c r="E53" s="5" t="n">
+        <v>0.061918</v>
+      </c>
+      <c r="F53" s="5" t="n">
+        <v>0.02507</v>
       </c>
       <c r="G53" s="5" t="n">
-        <v>-0.045477</v>
+        <v>0.028081</v>
       </c>
       <c r="H53" s="5" t="n">
-        <v>-0.034087</v>
+        <v>0.017129</v>
       </c>
     </row>
     <row r="54">
@@ -5183,12 +5033,12 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E54" t="inlineStr">
@@ -5201,11 +5051,13 @@
           <t>-</t>
         </is>
       </c>
-      <c r="G54" s="5" t="n">
-        <v>0</v>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="H54" s="5" t="n">
-        <v>0</v>
+        <v>-5e-06</v>
       </c>
     </row>
     <row r="55">
@@ -5216,26 +5068,34 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding –</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding – basic and diluted</t>
-        </is>
-      </c>
-      <c r="D55" t="inlineStr"/>
-      <c r="E55" s="5" t="n">
-        <v>7.593413</v>
-      </c>
-      <c r="F55" s="5" t="n">
-        <v>9.300000000000001</v>
+          <t>Interest income</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G55" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>0.0193</v>
       </c>
       <c r="H55" s="5" t="n">
-        <v>9.300000000000001</v>
+        <v>0.015016</v>
       </c>
     </row>
     <row r="56">
@@ -5246,15 +5106,19 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
-        </is>
-      </c>
-      <c r="D56" t="inlineStr"/>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E56" t="inlineStr">
         <is>
           <t>-</t>
@@ -5266,10 +5130,10 @@
         </is>
       </c>
       <c r="G56" s="5" t="n">
-        <v>0.546463</v>
+        <v>-0.045477</v>
       </c>
       <c r="H56" s="5" t="n">
-        <v>-0.259834</v>
+        <v>-0.034087</v>
       </c>
     </row>
     <row r="57">
@@ -5280,17 +5144,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
+          <t>Other Income (Expenses)</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
+          <t>Loss per share – basic and diluted $</t>
         </is>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>BasicEPS</t>
         </is>
       </c>
       <c r="E57" t="inlineStr">
@@ -5304,10 +5168,10 @@
         </is>
       </c>
       <c r="G57" s="5" t="n">
-        <v>-0.045477</v>
+        <v>0</v>
       </c>
       <c r="H57" s="5" t="n">
-        <v>-0.045477</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58">
@@ -5318,30 +5182,26 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
+          <t>Weighted average common shares outstanding –</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2024 9,300,000 $ 697,588 $ 108,709 $</t>
+          <t>Weighted average common shares outstanding – basic and diluted</t>
         </is>
       </c>
       <c r="D58" t="inlineStr"/>
-      <c r="E58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F58" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E58" s="5" t="n">
+        <v>7.593413</v>
+      </c>
+      <c r="F58" s="5" t="n">
+        <v>9.300000000000001</v>
       </c>
       <c r="G58" s="5" t="n">
-        <v>0.500986</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="H58" s="5" t="n">
-        <v>-0.305311</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="59">
@@ -5357,7 +5217,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2025 9,300,000 $ 697,588 $ 108,709 $</t>
+          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
         </is>
       </c>
       <c r="D59" t="inlineStr"/>
@@ -5372,10 +5232,10 @@
         </is>
       </c>
       <c r="G59" s="5" t="n">
-        <v>0.466899</v>
+        <v>0.546463</v>
       </c>
       <c r="H59" s="5" t="n">
-        <v>-0.339398</v>
+        <v>-0.259834</v>
       </c>
     </row>
     <row r="60">
@@ -5386,30 +5246,34 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ended                 Ended</t>
+          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Note May 31, 2023 May</t>
-        </is>
-      </c>
-      <c r="D60" t="inlineStr"/>
-      <c r="E60" s="5" t="n">
-        <v>0.002022</v>
-      </c>
-      <c r="F60" s="5" t="n">
-        <v>3.1e-05</v>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G60" s="5" t="n">
+        <v>-0.045477</v>
+      </c>
+      <c r="H60" s="5" t="n">
+        <v>-0.045477</v>
       </c>
     </row>
     <row r="61">
@@ -5420,32 +5284,30 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Corporate finance fees 6</t>
+          <t>Balance at May 31, 2024 9,300,000 $ 697,588 $ 108,709 $</t>
         </is>
       </c>
       <c r="D61" t="inlineStr"/>
-      <c r="E61" s="5" t="n">
-        <v>0.008</v>
+      <c r="E61" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G61" s="5" t="n">
+        <v>0.500986</v>
+      </c>
+      <c r="H61" s="5" t="n">
+        <v>-0.305311</v>
       </c>
     </row>
     <row r="62">
@@ -5456,32 +5318,30 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Number of shares         Amount          Reserves              Deficit                Total</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Marketing and investor relations expenses</t>
+          <t>Balance at May 31, 2025 9,300,000 $ 697,588 $ 108,709 $</t>
         </is>
       </c>
       <c r="D62" t="inlineStr"/>
-      <c r="E62" s="5" t="n">
-        <v>0.005058</v>
+      <c r="E62" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="G62" s="5" t="n">
+        <v>0.466899</v>
+      </c>
+      <c r="H62" s="5" t="n">
+        <v>-0.339398</v>
       </c>
     </row>
     <row r="63">
@@ -5492,22 +5352,20 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Operating Expenses</t>
+          <t>Ended                 Ended</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Share-based payments 6, 7</t>
+          <t>Note May 31, 2023 May</t>
         </is>
       </c>
       <c r="D63" t="inlineStr"/>
       <c r="E63" s="5" t="n">
-        <v>0.071297</v>
-      </c>
-      <c r="F63" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002022</v>
+      </c>
+      <c r="F63" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -5533,19 +5391,17 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Travel</t>
-        </is>
-      </c>
-      <c r="D64" t="inlineStr">
-        <is>
-          <t>SellingGeneralAndAdministration</t>
-        </is>
-      </c>
+          <t>Corporate finance fees 6</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr"/>
       <c r="E64" s="5" t="n">
-        <v>0.000102</v>
-      </c>
-      <c r="F64" s="5" t="n">
-        <v>0.001675</v>
+        <v>0.008</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -5566,24 +5422,22 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Foreign exchange loss</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>OtherIncomeExpense</t>
-        </is>
-      </c>
+          <t>Marketing and investor relations expenses</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr"/>
       <c r="E65" s="5" t="n">
-        <v>-1e-06</v>
-      </c>
-      <c r="F65" s="5" t="n">
-        <v>-1e-06</v>
+        <v>0.005058</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -5604,26 +5458,22 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Interest income</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>InterestIncomeNonOperating</t>
-        </is>
-      </c>
-      <c r="E66" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="F66" s="5" t="n">
-        <v>0.002118</v>
+          <t>Share-based payments 6, 7</t>
+        </is>
+      </c>
+      <c r="D66" t="inlineStr"/>
+      <c r="E66" s="5" t="n">
+        <v>0.071297</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -5644,24 +5494,24 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Other Expenses</t>
+          <t>Operating Expenses</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Other Expenses total</t>
+          <t>Travel</t>
         </is>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>OperatingExpense</t>
+          <t>SellingGeneralAndAdministration</t>
         </is>
       </c>
       <c r="E67" s="5" t="n">
-        <v>1e-06</v>
+        <v>0.000102</v>
       </c>
       <c r="F67" s="5" t="n">
-        <v>0.002117</v>
+        <v>0.001675</v>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -5687,19 +5537,19 @@
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Net and comprehensive loss $</t>
+          <t>Foreign exchange loss</t>
         </is>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NetIncome</t>
+          <t>OtherIncomeExpense</t>
         </is>
       </c>
       <c r="E68" s="5" t="n">
-        <v>-0.192185</v>
+        <v>-1e-06</v>
       </c>
       <c r="F68" s="5" t="n">
-        <v>-0.057473</v>
+        <v>-1e-06</v>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -5725,19 +5575,21 @@
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Loss per share – basic and diluted $</t>
+          <t>Interest income</t>
         </is>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>BasicEPS</t>
-        </is>
-      </c>
-      <c r="E69" s="5" t="n">
-        <v>-3e-08</v>
+          <t>InterestIncomeNonOperating</t>
+        </is>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="F69" s="5" t="n">
-        <v>-1e-08</v>
+        <v>0.002118</v>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -5758,20 +5610,24 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Weighted average common shares outstanding –</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>FOR THE YEAR ENDED MAY</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr"/>
+          <t>Other Expenses total</t>
+        </is>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>OperatingExpense</t>
+        </is>
+      </c>
       <c r="E70" s="5" t="n">
-        <v>0.002023</v>
+        <v>1e-06</v>
       </c>
       <c r="F70" s="5" t="n">
-        <v>3.1e-05</v>
+        <v>0.002117</v>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -5792,20 +5648,24 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2021 4,300,001 $ 285,001 $ - $</t>
-        </is>
-      </c>
-      <c r="D71" t="inlineStr"/>
+          <t>Net and comprehensive loss $</t>
+        </is>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
       <c r="E71" s="5" t="n">
-        <v>0.274825</v>
+        <v>-0.192185</v>
       </c>
       <c r="F71" s="5" t="n">
-        <v>-0.010176</v>
+        <v>-0.057473</v>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -5826,22 +5686,24 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+          <t>Other Expenses</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Share issuance for cash 5,000,000 500,000 -</t>
-        </is>
-      </c>
-      <c r="D72" t="inlineStr"/>
+          <t>Loss per share – basic and diluted $</t>
+        </is>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>BasicEPS</t>
+        </is>
+      </c>
       <c r="E72" s="5" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="F72" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>-3e-08</v>
+      </c>
+      <c r="F72" s="5" t="n">
+        <v>-1e-08</v>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -5862,22 +5724,20 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+          <t>Weighted average common shares outstanding –</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Share issuance fees - (50,000) -</t>
+          <t>FOR THE YEAR ENDED MAY</t>
         </is>
       </c>
       <c r="D73" t="inlineStr"/>
       <c r="E73" s="5" t="n">
-        <v>-0.05</v>
-      </c>
-      <c r="F73" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.002023</v>
+      </c>
+      <c r="F73" s="5" t="n">
+        <v>3.1e-05</v>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -5903,17 +5763,15 @@
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Issuance of stock options - - 71,297</t>
+          <t>Balance at May 31, 2021 4,300,001 $ 285,001 $ - $</t>
         </is>
       </c>
       <c r="D74" t="inlineStr"/>
       <c r="E74" s="5" t="n">
-        <v>0.071297</v>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+        <v>0.274825</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>-0.010176</v>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -5939,14 +5797,12 @@
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Issuance of agent’s options (37,412) 37,412</t>
+          <t>Share issuance for cash 5,000,000 500,000 -</t>
         </is>
       </c>
       <c r="D75" t="inlineStr"/>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="E75" s="5" t="n">
+        <v>0.5</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
@@ -5977,12 +5833,12 @@
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Repurchase and cancelation of incorporation share (1) (1) -</t>
+          <t>Share issuance fees - (50,000) -</t>
         </is>
       </c>
       <c r="D76" t="inlineStr"/>
       <c r="E76" s="5" t="n">
-        <v>-1e-06</v>
+        <v>-0.05</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
@@ -6013,19 +5869,17 @@
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Net loss - - -</t>
-        </is>
-      </c>
-      <c r="D77" t="inlineStr">
-        <is>
-          <t>NetIncome</t>
-        </is>
-      </c>
+          <t>Issuance of stock options - - 71,297</t>
+        </is>
+      </c>
+      <c r="D77" t="inlineStr"/>
       <c r="E77" s="5" t="n">
-        <v>-0.192185</v>
-      </c>
-      <c r="F77" s="5" t="n">
-        <v>-0.192185</v>
+        <v>0.071297</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -6051,15 +5905,19 @@
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2022 9,300,000 697,588 108,709</t>
+          <t>Issuance of agent’s options (37,412) 37,412</t>
         </is>
       </c>
       <c r="D78" t="inlineStr"/>
-      <c r="E78" s="5" t="n">
-        <v>0.603936</v>
-      </c>
-      <c r="F78" s="5" t="n">
-        <v>-0.202361</v>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -6085,22 +5943,130 @@
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
+          <t>Repurchase and cancelation of incorporation share (1) (1) -</t>
         </is>
       </c>
       <c r="D79" t="inlineStr"/>
       <c r="E79" s="5" t="n">
+        <v>-1e-06</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Net loss - - -</t>
+        </is>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>NetIncome</t>
+        </is>
+      </c>
+      <c r="E80" s="5" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="F80" s="5" t="n">
+        <v>-0.192185</v>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Balance at May 31, 2022 9,300,000 697,588 108,709</t>
+        </is>
+      </c>
+      <c r="D81" t="inlineStr"/>
+      <c r="E81" s="5" t="n">
+        <v>0.603936</v>
+      </c>
+      <c r="F81" s="5" t="n">
+        <v>-0.202361</v>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>income_statement</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Number of shares         Amount          Reserves                  Deficit                Total</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Balance at May 31, 2023 9,300,000 $ 697,588 $ 108,709 $</t>
+        </is>
+      </c>
+      <c r="D82" t="inlineStr"/>
+      <c r="E82" s="5" t="n">
         <v>0.546463</v>
       </c>
-      <c r="F79" s="5" t="n">
+      <c r="F82" s="5" t="n">
         <v>-0.259834</v>
       </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="H79" t="inlineStr">
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
         <is>
           <t>-</t>
         </is>
